--- a/artfynd/A 23102-2025 artfynd.xlsx
+++ b/artfynd/A 23102-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>18688</v>
       </c>
       <c r="B2" t="n">
-        <v>57576</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505218.8019262069</v>
+        <v>505219</v>
       </c>
       <c r="R2" t="n">
-        <v>6664154.008900867</v>
+        <v>6664154</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
